--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,54 @@
         <is>
           <t>is_active</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6a9169d9-2385-49fc-a24a-99b8eb9437e8</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>vasanth_025</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>vasanthkumar.2205155@srec.ac.in</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>$2b$12$7au0Ckf6KGx6bU/1QzG4e.B4eMAgVBdDheyI.ZSDYOZ4BC8xzD1m2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Vasanthkumar R</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>8610907778</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-04-15 14:42:16</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-04-15 14:44:24</t>
+        </is>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-04-15 14:44:24</t>
+          <t>2025-04-16 12:43:37</t>
         </is>
       </c>
       <c r="J2" t="b">

--- a/data/users.xlsx
+++ b/data/users.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2025-04-16 12:43:37</t>
+          <t>2025-04-18 20:52:02</t>
         </is>
       </c>
       <c r="J2" t="b">
